--- a/data/projects/56A0TXN/早期介入/交付预案/解析结果/预案草稿/8.3维保策略.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/解析结果/预案草稿/8.3维保策略.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,45 +439,35 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>maintYears</t>
+          <t>维保开始时间</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>maintTypeCode</t>
+          <t>维保结束时间</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>维保开始时间</t>
+          <t>产品EOS时间</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>维保结束时间</t>
+          <t>是否超EOS服务</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>产品EOS时间</t>
+          <t>超EOS审批结论</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>是否超EOS服务</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
-        <is>
-          <t>超EOS审批结论</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
         <is>
           <t>预案版本号</t>
         </is>
@@ -502,37 +492,33 @@
           <t>3 年 服务器介质保留服务</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>2026-12-13</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2029-12-12</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2029-12-12</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
           <t>自动解析</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -553,37 +539,33 @@
           <t>3 年 Hi-Care高级服务</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-12-13</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2029-12-12</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2029-12-12</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
           <t>自动解析</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
